--- a/gtm/field/prospects.xlsx
+++ b/gtm/field/prospects.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="Z4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr" s="0">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="Z20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr" s="0">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Z21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr" s="0">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="Z24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr" s="0">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="Z31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr" s="0">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="Z48" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr" s="0">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="Z50" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr" s="0">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="Z51" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr" s="0">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="Z54" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr" s="0">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="J4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr" s="2">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="J20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr" s="2">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="J21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="3">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="J4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr" s="3">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="J11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr" s="4">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="J8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr" s="3">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="J10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr" s="4">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="J11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr" s="4">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="J14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">39 € ist zu teuer (PRICE)</t>
+          <t xml:space="preserve">49 € ist zu teuer (PRICE)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr" s="4">
